--- a/paper_trades/dashboard_2026-06-01.xlsx
+++ b/paper_trades/dashboard_2026-06-01.xlsx
@@ -4228,7 +4228,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>محسوب في: 2026-06-01T11:52:44</t>
+          <t>محسوب في: 2026-06-01T12:31:18</t>
         </is>
       </c>
     </row>
